--- a/docs/reports/连通标注_2026-07-04_分表/9_关键人物.xlsx
+++ b/docs/reports/连通标注_2026-07-04_分表/9_关键人物.xlsx
@@ -1469,12 +1469,12 @@
       </c>
       <c r="L3" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="L4" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="L5" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="L6" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="L7" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="L8" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -1847,12 +1847,12 @@
       </c>
       <c r="L9" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L10" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -1973,12 +1973,12 @@
       </c>
       <c r="L11" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -2036,12 +2036,12 @@
       </c>
       <c r="L12" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="L13" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -2162,12 +2162,12 @@
       </c>
       <c r="L14" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="L15" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="L16" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -2351,12 +2351,12 @@
       </c>
       <c r="L17" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -2414,12 +2414,12 @@
       </c>
       <c r="L18" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -2477,12 +2477,12 @@
       </c>
       <c r="L19" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -2540,12 +2540,12 @@
       </c>
       <c r="L20" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="L21" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="L22" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -2729,12 +2729,12 @@
       </c>
       <c r="L23" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L24" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="L25" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -2918,12 +2918,12 @@
       </c>
       <c r="L26" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -2981,12 +2981,12 @@
       </c>
       <c r="L27" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L28" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="L29" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L30" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -3233,12 +3233,12 @@
       </c>
       <c r="L31" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -3296,12 +3296,12 @@
       </c>
       <c r="L32" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="L33" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -3422,12 +3422,12 @@
       </c>
       <c r="L34" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="L35" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="L36" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="L37" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -3674,12 +3674,12 @@
       </c>
       <c r="L38" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -3737,12 +3737,12 @@
       </c>
       <c r="L39" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="L40" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="L41" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="L42" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -3989,12 +3989,12 @@
       </c>
       <c r="L43" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="L44" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -4115,12 +4115,12 @@
       </c>
       <c r="L45" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L46" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4241,12 @@
       </c>
       <c r="L47" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L48" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="L49" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L50" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="L51" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -4556,12 +4556,12 @@
       </c>
       <c r="L52" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -4619,12 +4619,12 @@
       </c>
       <c r="L53" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -4682,12 +4682,12 @@
       </c>
       <c r="L54" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -4743,14 +4743,14 @@
           <t>Co-founder of Hugging Face; creator of the Transformers library. ｜ Hugging Face联创,Transformers库缔造者。</t>
         </is>
       </c>
-      <c r="L55" s="183" t="inlineStr">
-        <is>
-          <t>🔑 需API密钥</t>
+      <c r="L55" s="184" t="inlineStr">
+        <is>
+          <t>❌ 链接失效</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:HTTP 404</t>
         </is>
       </c>
     </row>
@@ -4808,12 +4808,12 @@
       </c>
       <c r="L56" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -4871,12 +4871,12 @@
       </c>
       <c r="L57" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -4932,14 +4932,14 @@
           <t>Founder of e/acc movement and Extropic; ex-Google quantum. ｜ e/acc运动与Extropic创始人,前谷歌量子工程师。</t>
         </is>
       </c>
-      <c r="L58" s="183" t="inlineStr">
-        <is>
-          <t>🔑 需API密钥</t>
+      <c r="L58" s="184" t="inlineStr">
+        <is>
+          <t>❌ 链接失效</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:HTTP 404</t>
         </is>
       </c>
     </row>
@@ -4997,12 +4997,12 @@
       </c>
       <c r="L59" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="L60" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -5123,12 +5123,12 @@
       </c>
       <c r="L61" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="L62" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -5249,12 +5249,12 @@
       </c>
       <c r="L63" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="L64" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -5375,12 +5375,12 @@
       </c>
       <c r="L65" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -5438,12 +5438,12 @@
       </c>
       <c r="L66" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -5501,12 +5501,12 @@
       </c>
       <c r="L67" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L68" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -5627,12 +5627,12 @@
       </c>
       <c r="L69" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L70" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="L71" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -5816,12 +5816,12 @@
       </c>
       <c r="L72" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L73" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -5942,12 +5942,12 @@
       </c>
       <c r="L74" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -6005,12 +6005,12 @@
       </c>
       <c r="L75" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="L76" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L77" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -6194,12 +6194,12 @@
       </c>
       <c r="L78" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -6257,12 +6257,12 @@
       </c>
       <c r="L79" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -6320,12 +6320,12 @@
       </c>
       <c r="L80" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -6383,12 +6383,12 @@
       </c>
       <c r="L81" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -6446,12 +6446,12 @@
       </c>
       <c r="L82" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="L83" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -6572,12 +6572,12 @@
       </c>
       <c r="L84" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -6635,12 +6635,12 @@
       </c>
       <c r="L85" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -6698,12 +6698,12 @@
       </c>
       <c r="L86" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="L87" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -6824,12 +6824,12 @@
       </c>
       <c r="L88" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="L89" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -6950,12 +6950,12 @@
       </c>
       <c r="L90" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -7013,12 +7013,12 @@
       </c>
       <c r="L91" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -7076,12 +7076,12 @@
       </c>
       <c r="L92" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L93" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -7202,12 +7202,12 @@
       </c>
       <c r="L94" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -7265,12 +7265,12 @@
       </c>
       <c r="L95" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="L96" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -7391,12 +7391,12 @@
       </c>
       <c r="L97" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="L98" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -7517,12 +7517,12 @@
       </c>
       <c r="L99" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -7578,14 +7578,14 @@
           <t>Founder of ChinaTalk on China tech and US-China policy. ｜ ChinaTalk创始人,中美科技与政策深度信源。</t>
         </is>
       </c>
-      <c r="L100" s="183" t="inlineStr">
-        <is>
-          <t>🔑 需API密钥</t>
+      <c r="L100" s="184" t="inlineStr">
+        <is>
+          <t>❌ 链接失效</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:HTTP 404</t>
         </is>
       </c>
     </row>
@@ -7643,12 +7643,12 @@
       </c>
       <c r="L101" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L102" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -7769,12 +7769,12 @@
       </c>
       <c r="L103" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="L104" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -7895,12 +7895,12 @@
       </c>
       <c r="L105" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L106" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="L107" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -8084,12 +8084,12 @@
       </c>
       <c r="L108" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -8147,12 +8147,12 @@
       </c>
       <c r="L109" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L110" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L111" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -8336,12 +8336,12 @@
       </c>
       <c r="L112" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L113" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -8462,12 +8462,12 @@
       </c>
       <c r="L114" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L115" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -8588,12 +8588,12 @@
       </c>
       <c r="L116" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -8651,12 +8651,12 @@
       </c>
       <c r="L117" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -8714,12 +8714,12 @@
       </c>
       <c r="L118" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -8777,12 +8777,12 @@
       </c>
       <c r="L119" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="L120" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -8903,12 +8903,12 @@
       </c>
       <c r="L121" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -8966,12 +8966,12 @@
       </c>
       <c r="L122" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -9029,12 +9029,12 @@
       </c>
       <c r="L123" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -9090,14 +9090,14 @@
           <t>Microcap investor surfacing under-covered small-cap ideas. ｜ 微型股投资人,挖掘被市场忽视的小盘机会。</t>
         </is>
       </c>
-      <c r="L124" s="183" t="inlineStr">
-        <is>
-          <t>🔑 需API密钥</t>
+      <c r="L124" s="184" t="inlineStr">
+        <is>
+          <t>❌ 链接失效</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:HTTP 404</t>
         </is>
       </c>
     </row>
@@ -9155,12 +9155,12 @@
       </c>
       <c r="L125" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -9218,12 +9218,12 @@
       </c>
       <c r="L126" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -9281,12 +9281,12 @@
       </c>
       <c r="L127" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -9344,12 +9344,12 @@
       </c>
       <c r="L128" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="L129" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -9470,12 +9470,12 @@
       </c>
       <c r="L130" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -9533,12 +9533,12 @@
       </c>
       <c r="L131" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -9596,12 +9596,12 @@
       </c>
       <c r="L132" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -9659,12 +9659,12 @@
       </c>
       <c r="L133" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -9722,12 +9722,12 @@
       </c>
       <c r="L134" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L135" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -9848,12 +9848,12 @@
       </c>
       <c r="L136" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -9911,12 +9911,12 @@
       </c>
       <c r="L137" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -9974,12 +9974,12 @@
       </c>
       <c r="L138" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -10037,12 +10037,12 @@
       </c>
       <c r="L139" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -10100,12 +10100,12 @@
       </c>
       <c r="L140" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -10163,12 +10163,12 @@
       </c>
       <c r="L141" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -10226,12 +10226,12 @@
       </c>
       <c r="L142" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="L143" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -10352,12 +10352,12 @@
       </c>
       <c r="L144" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -10415,12 +10415,12 @@
       </c>
       <c r="L145" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -10478,12 +10478,12 @@
       </c>
       <c r="L146" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -10541,12 +10541,12 @@
       </c>
       <c r="L147" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -10604,12 +10604,12 @@
       </c>
       <c r="L148" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -10667,12 +10667,12 @@
       </c>
       <c r="L149" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -10730,12 +10730,12 @@
       </c>
       <c r="L150" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -10793,12 +10793,12 @@
       </c>
       <c r="L151" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -10856,12 +10856,12 @@
       </c>
       <c r="L152" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -10919,12 +10919,12 @@
       </c>
       <c r="L153" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -10982,12 +10982,12 @@
       </c>
       <c r="L154" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="L155" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -11108,12 +11108,12 @@
       </c>
       <c r="L156" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -11171,12 +11171,12 @@
       </c>
       <c r="L157" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -11234,12 +11234,12 @@
       </c>
       <c r="L158" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -11297,12 +11297,12 @@
       </c>
       <c r="L159" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -11360,12 +11360,12 @@
       </c>
       <c r="L160" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L161" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -11486,12 +11486,12 @@
       </c>
       <c r="L162" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -11549,12 +11549,12 @@
       </c>
       <c r="L163" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -11612,12 +11612,12 @@
       </c>
       <c r="L164" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -11675,12 +11675,12 @@
       </c>
       <c r="L165" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -11738,12 +11738,12 @@
       </c>
       <c r="L166" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -11801,12 +11801,12 @@
       </c>
       <c r="L167" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -11864,12 +11864,12 @@
       </c>
       <c r="L168" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -11927,12 +11927,12 @@
       </c>
       <c r="L169" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -11990,12 +11990,12 @@
       </c>
       <c r="L170" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -12053,12 +12053,12 @@
       </c>
       <c r="L171" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -12114,14 +12114,14 @@
           <t>Former NY Fed trader, author of Central Banking 101. ｜ 前纽约联储交易员,货币与流动性机制权威解读者。</t>
         </is>
       </c>
-      <c r="L172" s="183" t="inlineStr">
-        <is>
-          <t>🔑 需API密钥</t>
+      <c r="L172" s="184" t="inlineStr">
+        <is>
+          <t>❌ 链接失效</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:HTTP 404</t>
         </is>
       </c>
     </row>
@@ -12179,12 +12179,12 @@
       </c>
       <c r="L173" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -12242,12 +12242,12 @@
       </c>
       <c r="L174" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -12303,14 +12303,14 @@
           <t>Macro and rates strategist on yield curves and policy. ｜ 宏观与利率策略师,研究收益率曲线与政策。</t>
         </is>
       </c>
-      <c r="L175" s="183" t="inlineStr">
-        <is>
-          <t>🔑 需API密钥</t>
+      <c r="L175" s="184" t="inlineStr">
+        <is>
+          <t>❌ 链接失效</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:HTTP 404</t>
         </is>
       </c>
     </row>
@@ -12368,12 +12368,12 @@
       </c>
       <c r="L176" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -12431,12 +12431,12 @@
       </c>
       <c r="L177" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -12494,12 +12494,12 @@
       </c>
       <c r="L178" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -12557,12 +12557,12 @@
       </c>
       <c r="L179" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -12620,12 +12620,12 @@
       </c>
       <c r="L180" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -12683,12 +12683,12 @@
       </c>
       <c r="L181" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -12746,12 +12746,12 @@
       </c>
       <c r="L182" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="L183" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -12872,12 +12872,12 @@
       </c>
       <c r="L184" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L185" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -12998,12 +12998,12 @@
       </c>
       <c r="L186" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="L187" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -13124,12 +13124,12 @@
       </c>
       <c r="L188" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -13187,12 +13187,12 @@
       </c>
       <c r="L189" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -13250,12 +13250,12 @@
       </c>
       <c r="L190" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -13313,12 +13313,12 @@
       </c>
       <c r="L191" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -13376,12 +13376,12 @@
       </c>
       <c r="L192" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L193" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -13502,12 +13502,12 @@
       </c>
       <c r="L194" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -13565,12 +13565,12 @@
       </c>
       <c r="L195" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L196" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -13691,12 +13691,12 @@
       </c>
       <c r="L197" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -13754,12 +13754,12 @@
       </c>
       <c r="L198" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -13817,12 +13817,12 @@
       </c>
       <c r="L199" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -13880,12 +13880,12 @@
       </c>
       <c r="L200" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -13943,12 +13943,12 @@
       </c>
       <c r="L201" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -14006,12 +14006,12 @@
       </c>
       <c r="L202" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -14069,12 +14069,12 @@
       </c>
       <c r="L203" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="L204" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -14195,12 +14195,12 @@
       </c>
       <c r="L205" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -14258,12 +14258,12 @@
       </c>
       <c r="L206" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -14321,12 +14321,12 @@
       </c>
       <c r="L207" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="L208" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -14447,12 +14447,12 @@
       </c>
       <c r="L209" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -14510,12 +14510,12 @@
       </c>
       <c r="L210" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -14573,12 +14573,12 @@
       </c>
       <c r="L211" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -14636,12 +14636,12 @@
       </c>
       <c r="L212" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -14699,12 +14699,12 @@
       </c>
       <c r="L213" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -14762,12 +14762,12 @@
       </c>
       <c r="L214" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -14825,12 +14825,12 @@
       </c>
       <c r="L215" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -14888,12 +14888,12 @@
       </c>
       <c r="L216" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -14951,12 +14951,12 @@
       </c>
       <c r="L217" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -15014,12 +15014,12 @@
       </c>
       <c r="L218" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -15077,12 +15077,12 @@
       </c>
       <c r="L219" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -15140,12 +15140,12 @@
       </c>
       <c r="L220" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -15203,12 +15203,12 @@
       </c>
       <c r="L221" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -15266,12 +15266,12 @@
       </c>
       <c r="L222" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -15329,12 +15329,12 @@
       </c>
       <c r="L223" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -15392,12 +15392,12 @@
       </c>
       <c r="L224" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -15455,12 +15455,12 @@
       </c>
       <c r="L225" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -15518,12 +15518,12 @@
       </c>
       <c r="L226" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -15581,12 +15581,12 @@
       </c>
       <c r="L227" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -15644,12 +15644,12 @@
       </c>
       <c r="L228" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -15707,12 +15707,12 @@
       </c>
       <c r="L229" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -15770,12 +15770,12 @@
       </c>
       <c r="L230" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -15833,12 +15833,12 @@
       </c>
       <c r="L231" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -15896,12 +15896,12 @@
       </c>
       <c r="L232" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -15959,12 +15959,12 @@
       </c>
       <c r="L233" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -16022,12 +16022,12 @@
       </c>
       <c r="L234" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -16085,12 +16085,12 @@
       </c>
       <c r="L235" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -16148,12 +16148,12 @@
       </c>
       <c r="L236" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -16211,12 +16211,12 @@
       </c>
       <c r="L237" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -16274,12 +16274,12 @@
       </c>
       <c r="L238" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -16337,7 +16337,7 @@
       </c>
       <c r="L239" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -16400,12 +16400,12 @@
       </c>
       <c r="L240" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -16463,12 +16463,12 @@
       </c>
       <c r="L241" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -16526,12 +16526,12 @@
       </c>
       <c r="L242" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -16589,12 +16589,12 @@
       </c>
       <c r="L243" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -16652,12 +16652,12 @@
       </c>
       <c r="L244" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="L245" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -16778,12 +16778,12 @@
       </c>
       <c r="L246" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -16841,12 +16841,12 @@
       </c>
       <c r="L247" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -16904,12 +16904,12 @@
       </c>
       <c r="L248" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -16967,12 +16967,12 @@
       </c>
       <c r="L249" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -17030,12 +17030,12 @@
       </c>
       <c r="L250" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L251" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -17156,12 +17156,12 @@
       </c>
       <c r="L252" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -17219,12 +17219,12 @@
       </c>
       <c r="L253" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -17282,12 +17282,12 @@
       </c>
       <c r="L254" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -17345,12 +17345,12 @@
       </c>
       <c r="L255" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -17408,12 +17408,12 @@
       </c>
       <c r="L256" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -17471,12 +17471,12 @@
       </c>
       <c r="L257" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -17534,12 +17534,12 @@
       </c>
       <c r="L258" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -17597,12 +17597,12 @@
       </c>
       <c r="L259" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -17660,12 +17660,12 @@
       </c>
       <c r="L260" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -17723,12 +17723,12 @@
       </c>
       <c r="L261" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -17786,12 +17786,12 @@
       </c>
       <c r="L262" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -17849,12 +17849,12 @@
       </c>
       <c r="L263" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -17912,12 +17912,12 @@
       </c>
       <c r="L264" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -17975,12 +17975,12 @@
       </c>
       <c r="L265" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -18038,12 +18038,12 @@
       </c>
       <c r="L266" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -18101,12 +18101,12 @@
       </c>
       <c r="L267" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -18164,12 +18164,12 @@
       </c>
       <c r="L268" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -18227,12 +18227,12 @@
       </c>
       <c r="L269" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -18290,12 +18290,12 @@
       </c>
       <c r="L270" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -18353,12 +18353,12 @@
       </c>
       <c r="L271" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -18416,12 +18416,12 @@
       </c>
       <c r="L272" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -18479,12 +18479,12 @@
       </c>
       <c r="L273" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -18542,12 +18542,12 @@
       </c>
       <c r="L274" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -18605,12 +18605,12 @@
       </c>
       <c r="L275" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -18668,12 +18668,12 @@
       </c>
       <c r="L276" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -18731,12 +18731,12 @@
       </c>
       <c r="L277" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -18794,12 +18794,12 @@
       </c>
       <c r="L278" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -18857,12 +18857,12 @@
       </c>
       <c r="L279" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -18920,12 +18920,12 @@
       </c>
       <c r="L280" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -18983,12 +18983,12 @@
       </c>
       <c r="L281" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -19046,12 +19046,12 @@
       </c>
       <c r="L282" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -19109,12 +19109,12 @@
       </c>
       <c r="L283" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -19172,12 +19172,12 @@
       </c>
       <c r="L284" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -19235,12 +19235,12 @@
       </c>
       <c r="L285" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -19298,12 +19298,12 @@
       </c>
       <c r="L286" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -19361,12 +19361,12 @@
       </c>
       <c r="L287" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
@@ -19424,12 +19424,12 @@
       </c>
       <c r="L288" s="183" t="inlineStr">
         <is>
-          <t>🔑 需API密钥</t>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(twitterapi.io)</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:$0.15/千条,按量无月费</t>
         </is>
       </c>
     </row>
